--- a/lessons/sorting/excels/remarks_git_star.xlsx
+++ b/lessons/sorting/excels/remarks_git_star.xlsx
@@ -162,12 +162,12 @@
     </comment>
     <comment ref="O4" authorId="0" shapeId="0">
       <text>
-        <t>-} (10:20:03.095), -flex (10:21:58.800), -direction (10:22:01.758), -column (10:22:03.223), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342), -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +justify (00:00:00), +content (00:00:00), +center (00:00:00), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-} (10:20:03.095) ~1.00, -flex (10:21:58.800) ~0.00, -direction (10:22:01.758) ~0.11, -column (10:22:03.223) ~0.17, +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342) ~1.00, -flex (10:57:30.392) ~1.00, -- (10:57:30.402) ~1.00, -end (10:57:30.432) ~0.00, -; (10:57:30.442) ~1.00, +justify (00:00:00), +content (00:00:00), +center (00:00:00), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q4" authorId="0" shapeId="0">
       <text>
-        <t>-i (10:38:53.739), -array (10:38:55.446), -createElement (10:39:45.021), -function (10:57:37.492), -bubbleSort (10:57:42.836), -( (10:57:43.053), -arr (10:57:49.140), -) (10:57:49.861), -{ (10:57:54.715), -} (10:58:35.895), -let (10:59:27.295), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -} (11:08:40.006), -( (11:09:55.956), -let (11:09:56.455), -i (11:09:56.677), -= (11:09:57.008), -0 (11:09:57.490), -; (11:09:57.512), -i (11:09:57.854), -&lt; (11:09:58.223), -bars (11:09:58.993), -. (11:09:59.214), -length (11:10:00.426), -; (11:10:00.634), -i (11:10:01.376), -+ (11:10:01.600), -+ (11:10:01.789), -) (11:10:01.880), -{ (11:10:02.609), -} (11:10:03.305), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -async (11:15:16.100), +1 (00:00:00), +arry (00:00:00), +cretaeElement (00:00:00), +function (00:00:00), +bubbleSort (00:00:00), +( (00:00:00), +arr (00:00:00), +) (00:00:00), +{ (00:00:00)</t>
+        <t>-i (10:38:53.739), -array (10:38:55.446) ~0.80, -createElement (10:39:45.021) ~0.85, -function (10:57:37.492) ~1.00, -bubbleSort (10:57:42.836) ~1.00, -( (10:57:43.053) ~1.00, -arr (10:57:49.140) ~1.00, -) (10:57:49.861) ~1.00, -{ (10:57:54.715) ~1.00, -} (10:58:35.895), -let (10:59:27.295), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -} (11:08:40.006), -( (11:09:55.956), -let (11:09:56.455), -i (11:09:56.677), -= (11:09:57.008), -0 (11:09:57.490), -; (11:09:57.512), -i (11:09:57.854) ~0.00, -&lt; (11:09:58.223), -bars (11:09:58.993), -. (11:09:59.214), -length (11:10:00.426), -; (11:10:00.634), -i (11:10:01.376), -+ (11:10:01.600), -+ (11:10:01.789), -) (11:10:01.880), -{ (11:10:02.609), -} (11:10:03.305), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -async (11:15:16.100), +1 (00:00:00), +arry (00:00:00), +cretaeElement (00:00:00), +function (00:00:00), +bubbleSort (00:00:00), +( (00:00:00), +arr (00:00:00), +) (00:00:00), +{ (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E5" authorId="0" shapeId="0">
@@ -187,12 +187,12 @@
     </comment>
     <comment ref="O5" authorId="0" shapeId="0">
       <text>
-        <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+        <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q5" authorId="0" shapeId="0">
       <text>
-        <t>-var (10:59:12.196), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -} (11:08:40.006), +let (00:00:00)</t>
+        <t>-var (10:59:12.196) ~0.00, +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -} (11:08:40.006), +let (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E9" authorId="0" shapeId="0">
@@ -212,17 +212,17 @@
     </comment>
     <comment ref="M9" authorId="0" shapeId="0">
       <text>
-        <t>-Visualizer (10:12:47.677), -Visualizer (10:13:16.993), +visualizer (00:00:00), +visualizer (00:00:00)</t>
+        <t>-Visualizer (10:12:47.677) ~0.90, -Visualizer (10:13:16.993) ~0.90, +visualizer (00:00:00), +visualizer (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O9" authorId="0" shapeId="0">
       <text>
-        <t>-} (10:17:11.029), -} (10:20:03.095), -flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00)</t>
+        <t>-} (10:17:11.029) ~1.00, -} (10:20:03.095) ~1.00, -flex (10:21:58.800) ~1.00, -- (10:21:58.984) ~1.00, -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q9" authorId="0" shapeId="0">
       <text>
-        <t>+bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -; (11:08:34.198), -updateBars (11:08:38.342), -getElementsByClassName (11:09:28.891), +function (00:00:00), +{ (00:00:00), +updatebars (00:00:00), +getElementByClassName (00:00:00), +} (00:00:00)</t>
+        <t>+bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -; (11:08:34.198) ~0.00, -updateBars (11:08:38.342) ~0.90, -getElementsByClassName (11:09:28.891) ~0.95, +function (00:00:00), +{ (00:00:00), +updatebars (00:00:00), +getElementByClassName (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E12" authorId="0" shapeId="0">
@@ -247,7 +247,7 @@
     </comment>
     <comment ref="O12" authorId="0" shapeId="0">
       <text>
-        <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+        <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E19" authorId="0" shapeId="0">
@@ -262,17 +262,17 @@
     </comment>
     <comment ref="M19" authorId="0" shapeId="0">
       <text>
-        <t>-&lt; (10:12:43.632), -title (10:12:44.512), -&gt; (10:12:44.622), -Sorting (10:12:45.778), -Visualizer (10:12:47.677), -&lt; (10:12:47.904), -/ (10:12:48.260), -title (10:12:49.434), -&gt; (10:12:49.841), +&lt; (00:00:00), +title (00:00:00), +&gt; (00:00:00), +Sorting (00:00:00), +Visualizer (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +title (00:00:00), +&gt; (00:00:00)</t>
+        <t>-&lt; (10:12:43.632) ~1.00, -title (10:12:44.512) ~1.00, -&gt; (10:12:44.622) ~1.00, -Sorting (10:12:45.778) ~1.00, -Visualizer (10:12:47.677) ~1.00, -&lt; (10:12:47.904) ~1.00, -/ (10:12:48.260) ~1.00, -title (10:12:49.434) ~1.00, -&gt; (10:12:49.841) ~1.00, +&lt; (00:00:00), +title (00:00:00), +&gt; (00:00:00), +Sorting (00:00:00), +Visualizer (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +title (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O19" authorId="0" shapeId="0">
       <text>
-        <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+        <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q19" authorId="0" shapeId="0">
       <text>
-        <t>-} (10:39:17.549), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -; (11:14:32.118), +} (00:00:00)</t>
+        <t>-} (10:39:17.549) ~1.00, +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -; (11:14:32.118), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E21" authorId="0" shapeId="0">
@@ -292,17 +292,17 @@
     </comment>
     <comment ref="M21" authorId="0" shapeId="0">
       <text>
-        <t>-Visualizer (10:12:47.677), +Visualiser (00:00:00)</t>
+        <t>-Visualizer (10:12:47.677) ~0.90, +Visualiser (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O21" authorId="0" shapeId="0">
       <text>
-        <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), -0px (10:48:03.827), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +0 (00:00:00)</t>
+        <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, -0px (10:48:03.827) ~0.33, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +0 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q21" authorId="0" shapeId="0">
       <text>
-        <t>-getElementsByClassName (11:09:28.891), -bars (11:09:58.993), -100 (11:14:24.924), +querySelectorAll (00:00:00), +. (00:00:00), +array (00:00:00), +10 (00:00:00)</t>
+        <t>-getElementsByClassName (11:09:28.891) ~0.18, -bars (11:09:58.993) ~0.20, -100 (11:14:24.924) ~0.67, +querySelectorAll (00:00:00), +. (00:00:00), +array (00:00:00), +10 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E24" authorId="0" shapeId="0">
@@ -322,7 +322,7 @@
     </comment>
     <comment ref="O24" authorId="0" shapeId="0">
       <text>
-        <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), -. (10:43:24.242), -bar (10:43:31.288), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +. (00:00:00), +bar (00:00:00)</t>
+        <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, -. (10:43:24.242) ~1.00, -bar (10:43:31.288) ~1.00, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +. (00:00:00), +bar (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q24" authorId="0" shapeId="0">
@@ -347,12 +347,12 @@
     </comment>
     <comment ref="O25" authorId="0" shapeId="0">
       <text>
-        <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+        <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q25" authorId="0" shapeId="0">
       <text>
-        <t>-length (10:38:57.372), -classList (10:42:32.670), -length (10:59:32.061), -getElementsByClassName (11:09:28.891), -length (11:10:00.426), -Promise (11:13:54.982), +lenght (00:00:00), +ClassList (00:00:00), +getElementByClassName (00:00:00), +lenght (00:00:00), +lenght (00:00:00), +promise (00:00:00)</t>
+        <t>-length (10:38:57.372) ~0.67, -classList (10:42:32.670) ~0.89, -length (10:59:32.061) ~0.67, -getElementsByClassName (11:09:28.891) ~0.95, -length (11:10:00.426) ~0.67, -Promise (11:13:54.982) ~0.86, +lenght (00:00:00), +ClassList (00:00:00), +getElementByClassName (00:00:00), +lenght (00:00:00), +lenght (00:00:00), +promise (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E30" authorId="0" shapeId="0">
@@ -372,7 +372,7 @@
     </comment>
     <comment ref="O30" authorId="0" shapeId="0">
       <text>
-        <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+        <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E31" authorId="0" shapeId="0">
@@ -392,17 +392,17 @@
     </comment>
     <comment ref="M31" authorId="0" shapeId="0">
       <text>
-        <t>-Sorting (10:12:45.778), +sorting (00:00:00)</t>
+        <t>-Sorting (10:12:45.778) ~0.86, +sorting (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O31" authorId="0" shapeId="0">
       <text>
-        <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+        <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q31" authorId="0" shapeId="0">
       <text>
-        <t>-for (10:59:26.374), -( (10:59:26.727), -let (10:59:27.295), -i (10:59:27.677), -= (10:59:27.952), -1 (10:59:28.458), -; (10:59:28.738), -i (10:59:29.253), -&lt; (10:59:29.652), -arr (10:59:30.525), -. (10:59:30.766), -length (10:59:32.061), -; (10:59:32.305), -i (10:59:32.661), -+ (10:59:32.869), -+ (10:59:33.126), -) (10:59:33.350), -{ (10:59:35.506), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +arr (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00)</t>
+        <t>-for (10:59:26.374) ~1.00, -( (10:59:26.727) ~1.00, -let (10:59:27.295) ~1.00, -i (10:59:27.677) ~1.00, -= (10:59:27.952) ~1.00, -1 (10:59:28.458) ~0.00, -; (10:59:28.738) ~1.00, -i (10:59:29.253) ~1.00, -&lt; (10:59:29.652) ~1.00, -arr (10:59:30.525) ~1.00, -. (10:59:30.766) ~1.00, -length (10:59:32.061) ~1.00, -; (10:59:32.305) ~1.00, -i (10:59:32.661) ~1.00, -+ (10:59:32.869) ~1.00, -+ (10:59:33.126) ~1.00, -) (10:59:33.350) ~1.00, -{ (10:59:35.506) ~1.00, +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +arr (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E36" authorId="0" shapeId="0">
@@ -422,17 +422,17 @@
     </comment>
     <comment ref="M36" authorId="0" shapeId="0">
       <text>
-        <t>-Sorting (10:13:13.802), +/ (00:00:00), +sorting (00:00:00)</t>
+        <t>-Sorting (10:13:13.802) ~0.86, +/ (00:00:00), +sorting (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O36" authorId="0" shapeId="0">
       <text>
-        <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+        <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q36" authorId="0" shapeId="0">
       <text>
-        <t>-50 (10:27:50.527), -. (10:31:30.292), -. (10:38:55.684), -. (10:40:28.151), -arr (11:01:09.861), -; (11:01:10.683), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -; (11:10:17.104), -Promise (11:13:54.982), +20 (00:00:00), +, (00:00:00), +bubblesort (00:00:00), +, (00:00:00), +, (00:00:00), +aee (00:00:00), +promise (00:00:00)</t>
+        <t>-50 (10:27:50.527) ~0.50, -. (10:31:30.292) ~0.00, -. (10:38:55.684) ~0.00, -. (10:40:28.151) ~0.00, -arr (11:01:09.861) ~0.33, -; (11:01:10.683), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -; (11:10:17.104), -Promise (11:13:54.982) ~0.86, +20 (00:00:00), +, (00:00:00), +bubblesort (00:00:00), +, (00:00:00), +, (00:00:00), +aee (00:00:00), +promise (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E42" authorId="0" shapeId="0">
@@ -452,12 +452,12 @@
     </comment>
     <comment ref="O42" authorId="0" shapeId="0">
       <text>
-        <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +coloumn (00:00:00), +; (00:00:00)</t>
+        <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952), -column (10:22:03.223) ~0.86, -; (10:22:03.455) ~1.00, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +coloumn (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q42" authorId="0" shapeId="0">
       <text>
-        <t>-let (10:38:51.733), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -let (11:09:56.455), -bars (11:09:58.993), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -updateBars (11:12:30.664), -( (11:12:30.752), -) (11:12:30.906), -; (11:12:31.204), -await (11:13:47.348), -new (11:13:53.570), -Promise (11:13:54.982), -( (11:13:55.301), -resolve (11:13:59.055), -= (11:14:16.118), -&gt; (11:14:16.408), -setTimeout (11:14:18.857), -( (11:14:19.066), -resolve (11:14:23.324), -, (11:14:23.491), -100 (11:14:24.924), -) (11:14:31.103), -) (11:14:31.475), -; (11:14:32.118), -async (11:15:16.100), +array (00:00:00)</t>
+        <t>-let (10:38:51.733), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -let (11:09:56.455), -bars (11:09:58.993) ~0.20, -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -updateBars (11:12:30.664), -( (11:12:30.752), -) (11:12:30.906), -; (11:12:31.204), -await (11:13:47.348), -new (11:13:53.570), -Promise (11:13:54.982), -( (11:13:55.301), -resolve (11:13:59.055), -= (11:14:16.118), -&gt; (11:14:16.408), -setTimeout (11:14:18.857), -( (11:14:19.066), -resolve (11:14:23.324), -, (11:14:23.491), -100 (11:14:24.924), -) (11:14:31.103), -) (11:14:31.475), -; (11:14:32.118), -async (11:15:16.100), +array (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D45" authorId="0" shapeId="0">
@@ -482,12 +482,12 @@
     </comment>
     <comment ref="O45" authorId="0" shapeId="0">
       <text>
-        <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+        <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q45" authorId="0" shapeId="0">
       <text>
-        <t>-} (10:39:17.549), -; (11:10:17.104), +} (00:00:00)</t>
+        <t>-} (10:39:17.549) ~1.00, -; (11:10:17.104), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E46" authorId="0" shapeId="0">
@@ -507,7 +507,7 @@
     </comment>
     <comment ref="O46" authorId="0" shapeId="0">
       <text>
-        <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), -display (10:47:38.305), -flex (10:47:39.551), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +red* (10:50:09.332), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+        <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, -display (10:47:38.305), -flex (10:47:39.551), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +red* (10:50:09.332), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E48" authorId="0" shapeId="0">
@@ -522,17 +522,17 @@
     </comment>
     <comment ref="M48" authorId="0" shapeId="0">
       <text>
-        <t>-title (10:12:49.434), -Visualizer (10:13:16.993), +tittle (00:00:00), +visualizer (00:00:00)</t>
+        <t>-title (10:12:49.434) ~0.83, -Visualizer (10:13:16.993) ~0.90, +tittle (00:00:00), +visualizer (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O48" authorId="0" shapeId="0">
       <text>
-        <t>-} (10:20:03.095), -flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), -display (10:47:38.305), -flex (10:47:39.551), -; (10:47:39.811), -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), -; (10:48:07.569), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +red* (10:50:09.332), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342), -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-} (10:20:03.095) ~1.00, -flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, -display (10:47:38.305), -flex (10:47:39.551), -; (10:47:39.811), -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), -; (10:48:07.569), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +red* (10:50:09.332), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342) ~1.00, -flex (10:57:30.392) ~1.00, -- (10:57:30.402) ~1.00, -end (10:57:30.432) ~0.11, -; (10:57:30.442), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q48" authorId="0" shapeId="0">
       <text>
-        <t>-array (10:28:45.898), -const (10:37:42.386), -visualizer (10:37:44.631), -= (10:37:45.082), -document (10:37:47.323), -. (10:37:47.760), -getElementById (10:38:03.158), -" (10:38:19.019), -vis (10:38:19.926), -- (10:38:20.217), -123456 (10:38:22.251), -" (10:38:22.629), +bubbleSort* (11:08:31.581), -array (11:08:34.178), -getElementsByClassName (11:09:28.891), +arry (00:00:00), +arry (00:00:00), +const (00:00:00), +visualizer (00:00:00), += (00:00:00), +documnet (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
+        <t>-array (10:28:45.898) ~0.80, -const (10:37:42.386) ~1.00, -visualizer (10:37:44.631) ~1.00, -= (10:37:45.082) ~1.00, -document (10:37:47.323) ~0.75, -. (10:37:47.760) ~1.00, -getElementById (10:38:03.158) ~1.00, -" (10:38:19.019) ~1.00, -vis (10:38:19.926) ~1.00, -- (10:38:20.217) ~1.00, -123456 (10:38:22.251) ~1.00, -" (10:38:22.629) ~1.00, +bubbleSort* (11:08:31.581), -array (11:08:34.178) ~0.80, -getElementsByClassName (11:09:28.891) ~0.95, +arry (00:00:00), +arry (00:00:00), +const (00:00:00), +visualizer (00:00:00), += (00:00:00), +documnet (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E50" authorId="0" shapeId="0">
@@ -552,17 +552,17 @@
     </comment>
     <comment ref="M50" authorId="0" shapeId="0">
       <text>
-        <t>-html (10:12:23.484), +htm (00:00:00)</t>
+        <t>-html (10:12:23.484) ~0.75, +htm (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O50" authorId="0" shapeId="0">
       <text>
-        <t>-} (10:20:03.095), -flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), -- (10:57:30.402), -end (10:57:30.432), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-} (10:20:03.095) ~1.00, -flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, -- (10:57:30.402) ~1.00, -end (10:57:30.432) ~0.11, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q50" authorId="0" shapeId="0">
       <text>
-        <t>-bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -getElementsByClassName (11:09:28.891), -100 (11:14:24.924), +getElementsByClassname (00:00:00), +10 (00:00:00)</t>
+        <t>-bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -getElementsByClassName (11:09:28.891) ~0.95, -100 (11:14:24.924) ~0.67, +getElementsByClassname (00:00:00), +10 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E51" authorId="0" shapeId="0">
@@ -582,7 +582,7 @@
     </comment>
     <comment ref="O51" authorId="0" shapeId="0">
       <text>
-        <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+        <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E56" authorId="0" shapeId="0">
@@ -602,17 +602,17 @@
     </comment>
     <comment ref="M56" authorId="0" shapeId="0">
       <text>
-        <t>-&lt; (10:12:43.632), -title (10:12:44.512), -&gt; (10:12:44.622), -&lt; (10:12:47.904), -/ (10:12:48.260), -title (10:12:49.434), -&gt; (10:12:49.841), -Sorting (10:13:13.802), -Visualizer (10:13:16.993), -&lt; (10:13:17.335), -/ (10:13:17.789), -h1 (10:13:18.123), -&gt; (10:13:18.254), +Sorting (00:00:00), +Visualizer (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +h1 (00:00:00), +&gt; (00:00:00)</t>
+        <t>-&lt; (10:12:43.632), -title (10:12:44.512), -&gt; (10:12:44.622), -&lt; (10:12:47.904), -/ (10:12:48.260), -title (10:12:49.434), -&gt; (10:12:49.841), -Sorting (10:13:13.802) ~1.00, -Visualizer (10:13:16.993) ~1.00, -&lt; (10:13:17.335) ~1.00, -/ (10:13:17.789) ~1.00, -h1 (10:13:18.123) ~1.00, -&gt; (10:13:18.254) ~1.00, +Sorting (00:00:00), +Visualizer (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +h1 (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O56" authorId="0" shapeId="0">
       <text>
-        <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+        <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q56" authorId="0" shapeId="0">
       <text>
-        <t>-; (10:50:48.660), -100 (11:14:24.924), +10 (00:00:00)</t>
+        <t>-; (10:50:48.660), -100 (11:14:24.924) ~0.67, +10 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E59" authorId="0" shapeId="0">
@@ -632,17 +632,17 @@
     </comment>
     <comment ref="O59" authorId="0" shapeId="0">
       <text>
-        <t>-} (10:20:03.095), -flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342), -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +flex (00:00:00), +- (00:00:00), +end (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+        <t>-} (10:20:03.095) ~1.00, -flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952), -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, -align (10:57:30.272) ~1.00, -- (10:57:30.282) ~1.00, -items (10:57:30.332), -: (10:57:30.342) ~1.00, -flex (10:57:30.392) ~1.00, -- (10:57:30.402) ~1.00, -end (10:57:30.432) ~1.00, -; (10:57:30.442) ~1.00, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +flex (00:00:00), +- (00:00:00), +end (00:00:00), +; (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q59" authorId="0" shapeId="0">
       <text>
-        <t>-length (10:38:57.372), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -getElementsByClassName (11:09:28.891), -; (11:14:32.118), +lenght (00:00:00), +getElementsByClassname (00:00:00)</t>
+        <t>-length (10:38:57.372) ~0.67, +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -getElementsByClassName (11:09:28.891) ~0.95, -; (11:14:32.118), +lenght (00:00:00), +getElementsByClassname (00:00:00)</t>
       </text>
     </comment>
     <comment ref="D62" authorId="0" shapeId="0">
       <text>
-        <t>Short name part(s) not auto-redacted (verify manually): De</t>
+        <t>Short name part(s) not auto-redacted</t>
       </text>
     </comment>
     <comment ref="E62" authorId="0" shapeId="0">
@@ -662,7 +662,7 @@
     </comment>
     <comment ref="O62" authorId="0" shapeId="0">
       <text>
-        <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+        <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E66" authorId="0" shapeId="0">
@@ -682,7 +682,7 @@
     </comment>
     <comment ref="O66" authorId="0" shapeId="0">
       <text>
-        <t>-} (10:20:03.095), -flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), -7px (10:43:39.527), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +} (00:00:00), +700px (00:00:00)</t>
+        <t>-} (10:20:03.095) ~1.00, -flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, -7px (10:43:39.527) ~0.60, +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +} (00:00:00), +700px (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q66" authorId="0" shapeId="0">
@@ -707,12 +707,12 @@
     </comment>
     <comment ref="O68" authorId="0" shapeId="0">
       <text>
-        <t>-height (10:20:07.891), -: (10:20:07.983), -200px (10:20:09.051), -; (10:20:09.451), -0px (10:48:03.827), +;* (10:50:09.333), +height (00:00:00), +: (00:00:00), +200px (00:00:00), +background (00:00:00), +: (00:00:00), +red (00:00:00), +; (00:00:00), +0 (00:00:00)</t>
+        <t>-height (10:20:07.891) ~1.00, -: (10:20:07.983) ~1.00, -200px (10:20:09.051) ~1.00, -; (10:20:09.451), -0px (10:48:03.827) ~0.33, +;* (10:50:09.333), +height (00:00:00), +: (00:00:00), +200px (00:00:00), +background (00:00:00), +: (00:00:00), +red (00:00:00), +; (00:00:00), +0 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q68" authorId="0" shapeId="0">
       <text>
-        <t>-function (10:57:37.492), -bubbleSort (10:57:42.836), -( (10:57:43.053), -arr (10:57:49.140), -) (10:57:49.861), -{ (10:57:54.715), -1 (10:59:28.458), -- (10:59:44.058), -1 (10:59:44.656), -- (11:01:07.252), -1 (11:01:07.757), -bubbleSort (11:08:34.118), -array (11:08:34.178), -function (11:08:36.630), -updateBars (11:08:38.342), -( (11:08:38.511), -) (11:08:38.687), -{ (11:08:39.319), -const (11:09:21.850), -bars (11:09:22.876), -= (11:09:23.405), -document (11:09:24.920), -. (11:09:25.072), -getElementsByClassName (11:09:28.891), -( (11:09:28.949), -" (11:09:29.056), -bar (11:09:29.764), -" (11:09:29.897), -) (11:09:29.998), -; (11:09:30.476), -for (11:09:55.616), -( (11:09:55.956), -let (11:09:56.455), -i (11:09:56.677), -= (11:09:57.008), -0 (11:09:57.490), -; (11:09:57.512), -i (11:09:57.854), -&lt; (11:09:58.223), -bars (11:09:58.993), -. (11:09:59.214), -length (11:10:00.426), -; (11:10:00.634), -i (11:10:01.376), -+ (11:10:01.600), -+ (11:10:01.789), -) (11:10:01.880), -{ (11:10:02.609), -updateBars (11:12:30.664), -await (11:13:47.348), -new (11:13:53.570), -Promise (11:13:54.982), -( (11:13:55.301), -resolve (11:13:59.055), -= (11:14:16.118), -&gt; (11:14:16.408), -setTimeout (11:14:18.857), -( (11:14:19.066), -resolve (11:14:23.324), -, (11:14:23.491), -100 (11:14:24.924), -) (11:14:31.103), -) (11:14:31.475), -; (11:14:32.118), -async (11:15:16.100), +function (00:00:00), +updataBars (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +visualizer (00:00:00), +. (00:00:00), +querySelectorAll (00:00:00), +" (00:00:00), +. (00:00:00), +bar (00:00:00), +" (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +array (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +async (00:00:00), +function (00:00:00), +bubblesort (00:00:00), +( (00:00:00), +arr (00:00:00), +) (00:00:00), +{ (00:00:00), +0 (00:00:00), +- (00:00:00), +1 (00:00:00), ++ (00:00:00), +1 (00:00:00), ++ (00:00:00), +1 (00:00:00), ++ (00:00:00), +1 (00:00:00), +updataBars (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +10 (00:00:00), +) (00:00:00)</t>
+        <t>-function (10:57:37.492) ~1.00, -bubbleSort (10:57:42.836) ~0.90, -( (10:57:43.053) ~1.00, -arr (10:57:49.140) ~1.00, -) (10:57:49.861) ~1.00, -{ (10:57:54.715) ~1.00, -1 (10:59:28.458) ~0.00, -- (10:59:44.058), -1 (10:59:44.656) ~1.00, -- (11:01:07.252) ~0.00, -1 (11:01:07.757) ~1.00, -bubbleSort (11:08:34.118) ~0.20, -array (11:08:34.178), -function (11:08:36.630), -updateBars (11:08:38.342) ~0.90, -( (11:08:38.511) ~1.00, -) (11:08:38.687) ~1.00, -{ (11:08:39.319) ~1.00, -const (11:09:21.850) ~1.00, -bars (11:09:22.876) ~1.00, -= (11:09:23.405) ~1.00, -document (11:09:24.920) ~0.10, -. (11:09:25.072) ~1.00, -getElementsByClassName (11:09:28.891) ~0.18, -( (11:09:28.949) ~0.00, -" (11:09:29.056) ~1.00, -bar (11:09:29.764) ~1.00, -" (11:09:29.897) ~1.00, -) (11:09:29.998), -; (11:09:30.476), -for (11:09:55.616) ~1.00, -( (11:09:55.956) ~1.00, -let (11:09:56.455) ~1.00, -i (11:09:56.677) ~1.00, -= (11:09:57.008) ~1.00, -0 (11:09:57.490) ~1.00, -; (11:09:57.512) ~1.00, -i (11:09:57.854) ~1.00, -&lt; (11:09:58.223) ~1.00, -bars (11:09:58.993) ~0.20, -. (11:09:59.214) ~1.00, -length (11:10:00.426) ~1.00, -; (11:10:00.634) ~1.00, -i (11:10:01.376) ~1.00, -+ (11:10:01.600) ~1.00, -+ (11:10:01.789) ~1.00, -) (11:10:01.880) ~1.00, -{ (11:10:02.609) ~1.00, -updateBars (11:12:30.664) ~0.90, -await (11:13:47.348) ~1.00, -new (11:13:53.570) ~1.00, -Promise (11:13:54.982) ~1.00, -( (11:13:55.301) ~1.00, -resolve (11:13:59.055) ~1.00, -= (11:14:16.118) ~1.00, -&gt; (11:14:16.408) ~1.00, -setTimeout (11:14:18.857) ~1.00, -( (11:14:19.066) ~1.00, -resolve (11:14:23.324) ~1.00, -, (11:14:23.491) ~1.00, -100 (11:14:24.924) ~0.67, -) (11:14:31.103) ~1.00, -) (11:14:31.475), -; (11:14:32.118), -async (11:15:16.100) ~1.00, +function (00:00:00), +updataBars (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +visualizer (00:00:00), +. (00:00:00), +querySelectorAll (00:00:00), +" (00:00:00), +. (00:00:00), +bar (00:00:00), +" (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +array (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +async (00:00:00), +function (00:00:00), +bubblesort (00:00:00), +( (00:00:00), +arr (00:00:00), +) (00:00:00), +{ (00:00:00), +0 (00:00:00), +- (00:00:00), +1 (00:00:00), ++ (00:00:00), +1 (00:00:00), ++ (00:00:00), +1 (00:00:00), ++ (00:00:00), +1 (00:00:00), +updataBars (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +10 (00:00:00), +) (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E70" authorId="0" shapeId="0">
@@ -732,17 +732,17 @@
     </comment>
     <comment ref="M70" authorId="0" shapeId="0">
       <text>
-        <t>-DOCTYPE (10:12:14.338), -Visualizer (10:12:47.677), -Sorting (10:13:13.802), -Visualizer (10:13:16.993), -&lt; (10:27:15.917), +Doctype (00:00:00), +visualizer (00:00:00), +sorting (00:00:00), +visualizer (00:00:00)</t>
+        <t>-DOCTYPE (10:12:14.338) ~0.14, -Visualizer (10:12:47.677) ~0.90, -Sorting (10:13:13.802) ~0.86, -Visualizer (10:13:16.993) ~0.90, -&lt; (10:27:15.917), +Doctype (00:00:00), +visualizer (00:00:00), +sorting (00:00:00), +visualizer (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O70" authorId="0" shapeId="0">
       <text>
-        <t>-200px (10:20:09.051), -flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), -background (10:44:24.231), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +500px (00:00:00), +Background (00:00:00)</t>
+        <t>-200px (10:20:09.051) ~0.80, -flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, -background (10:44:24.231) ~0.90, +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +500px (00:00:00), +Background (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q70" authorId="0" shapeId="0">
       <text>
-        <t>-bubbleSort (10:57:42.836), -i (10:59:29.253), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -&lt; (11:09:58.223), -bars (11:09:58.993), -i (11:10:01.376), -Promise (11:13:54.982), +&gt; (00:00:00), +bats (00:00:00), +bubblesort (00:00:00), +promise (00:00:00)</t>
+        <t>-bubbleSort (10:57:42.836) ~0.90, -i (10:59:29.253), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -&lt; (11:09:58.223) ~0.00, -bars (11:09:58.993) ~0.75, -i (11:10:01.376), -Promise (11:13:54.982) ~0.86, +&gt; (00:00:00), +bats (00:00:00), +bubblesort (00:00:00), +promise (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E71" authorId="0" shapeId="0">
@@ -757,7 +757,7 @@
     </comment>
     <comment ref="O71" authorId="0" shapeId="0">
       <text>
-        <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+        <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q71" authorId="0" shapeId="0">
@@ -782,17 +782,17 @@
     </comment>
     <comment ref="M72" authorId="0" shapeId="0">
       <text>
-        <t>-title (10:12:49.434), -Visualizer (10:13:16.993), -123456 (10:18:40.665), +tittle (00:00:00), +visualizer (00:00:00), +654321 (00:00:00)</t>
+        <t>-title (10:12:49.434) ~0.83, -Visualizer (10:13:16.993) ~0.90, -123456 (10:18:40.665) ~0.00, +tittle (00:00:00), +visualizer (00:00:00), +654321 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O72" authorId="0" shapeId="0">
       <text>
-        <t>-# (10:19:53.296), -vis (10:19:54.003), -- (10:19:54.226), -123456 (10:19:55.544), -{ (10:20:02.452), -} (10:20:03.095), -flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), -display (10:47:38.305), -flex (10:47:39.551), -; (10:47:39.811), -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), -; (10:48:07.569), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +red* (10:50:09.332), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342), -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +654321 (00:00:00), +{ (00:00:00), +} (00:00:00)</t>
+        <t>-# (10:19:53.296) ~1.00, -vis (10:19:54.003) ~1.00, -- (10:19:54.226) ~1.00, -123456 (10:19:55.544) ~0.00, -{ (10:20:02.452) ~1.00, -} (10:20:03.095) ~1.00, -flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, -display (10:47:38.305), -flex (10:47:39.551), -; (10:47:39.811), -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), -; (10:48:07.569), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +red* (10:50:09.332), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342) ~1.00, -flex (10:57:30.392) ~1.00, -- (10:57:30.402) ~1.00, -end (10:57:30.432) ~0.11, -; (10:57:30.442), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +654321 (00:00:00), +{ (00:00:00), +} (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q72" authorId="0" shapeId="0">
       <text>
-        <t>-array (10:28:45.898), -const (10:37:42.386), -visualizer (10:37:44.631), -= (10:37:45.082), -document (10:37:47.323), -. (10:37:47.760), -getElementById (10:38:03.158), -" (10:38:19.019), -vis (10:38:19.926), -- (10:38:20.217), -123456 (10:38:22.251), -" (10:38:22.629), +bubbleSort* (11:08:31.581), -array (11:08:34.178), -getElementsByClassName (11:09:28.891), +arry (00:00:00), +arry (00:00:00), +const (00:00:00), +visualizer (00:00:00), += (00:00:00), +documnet (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +654321 (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
+        <t>-array (10:28:45.898) ~0.80, -const (10:37:42.386) ~1.00, -visualizer (10:37:44.631) ~1.00, -= (10:37:45.082) ~1.00, -document (10:37:47.323) ~0.75, -. (10:37:47.760) ~1.00, -getElementById (10:38:03.158) ~1.00, -" (10:38:19.019) ~1.00, -vis (10:38:19.926) ~1.00, -- (10:38:20.217) ~1.00, -123456 (10:38:22.251) ~0.00, -" (10:38:22.629) ~1.00, +bubbleSort* (11:08:31.581), -array (11:08:34.178) ~0.80, -getElementsByClassName (11:09:28.891) ~0.95, +arry (00:00:00), +arry (00:00:00), +const (00:00:00), +visualizer (00:00:00), += (00:00:00), +documnet (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +654321 (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E73" authorId="0" shapeId="0">
@@ -812,7 +812,7 @@
     </comment>
     <comment ref="O73" authorId="0" shapeId="0">
       <text>
-        <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+        <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E75" authorId="0" shapeId="0">
@@ -827,12 +827,12 @@
     </comment>
     <comment ref="O75" authorId="0" shapeId="0">
       <text>
-        <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342), -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+        <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342) ~1.00, -flex (10:57:30.392) ~1.00, -- (10:57:30.402) ~1.00, -end (10:57:30.432) ~0.11, -; (10:57:30.442), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q75" authorId="0" shapeId="0">
       <text>
-        <t>-createElement (10:39:45.021), -visualizer (10:40:27.992), -. (10:40:28.151), -appendChild (10:40:30.229), -( (10:40:30.435), -bar (10:40:31.317), -) (10:40:31.505), -; (10:40:32.101), -bubbleSort (10:57:42.836), -&gt; (10:59:45.546), -arr (10:59:46.616), -[ (10:59:46.969), -i (10:59:47.212), -] (10:59:47.751), -- (11:01:03.607), -1 (11:01:04.198), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -function (11:08:36.630), -updateBars (11:08:38.342), -( (11:08:38.511), -) (11:08:38.687), -{ (11:08:39.319), -getElementsByClassName (11:09:28.891), -; (11:09:57.512), -i (11:09:57.854), -bars (11:09:58.993), -} (11:10:03.305), -setTimeout (11:14:18.857), +createrElement (00:00:00), +function (00:00:00), +updatebars (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +get (00:00:00), +ElementsByClassName (00:00:00), +array (00:00:00), +bubblesort (00:00:00), +setTimeOut (00:00:00)</t>
+        <t>-createElement (10:39:45.021) ~0.93, -visualizer (10:40:27.992), -. (10:40:28.151), -appendChild (10:40:30.229), -( (10:40:30.435), -bar (10:40:31.317), -) (10:40:31.505), -; (10:40:32.101), -bubbleSort (10:57:42.836) ~0.90, -&gt; (10:59:45.546), -arr (10:59:46.616), -[ (10:59:46.969), -i (10:59:47.212), -] (10:59:47.751), -- (11:01:03.607), -1 (11:01:04.198), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -bubbleSort (11:08:34.118), -( (11:08:34.128) ~1.00, -array (11:08:34.178), -) (11:08:34.188) ~1.00, -; (11:08:34.198), -function (11:08:36.630) ~1.00, -updateBars (11:08:38.342) ~0.90, -( (11:08:38.511), -) (11:08:38.687), -{ (11:08:39.319) ~1.00, -getElementsByClassName (11:09:28.891) ~0.86, -; (11:09:57.512), -i (11:09:57.854), -bars (11:09:58.993) ~0.20, -} (11:10:03.305), -setTimeout (11:14:18.857) ~0.90, +createrElement (00:00:00), +function (00:00:00), +updatebars (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +get (00:00:00), +ElementsByClassName (00:00:00), +array (00:00:00), +bubblesort (00:00:00), +setTimeOut (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E78" authorId="0" shapeId="0">
@@ -852,7 +852,7 @@
     </comment>
     <comment ref="O78" authorId="0" shapeId="0">
       <text>
-        <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+        <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q78" authorId="0" shapeId="0">
@@ -877,12 +877,12 @@
     </comment>
     <comment ref="O79" authorId="0" shapeId="0">
       <text>
-        <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+        <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q79" authorId="0" shapeId="0">
       <text>
-        <t>-; (10:50:48.660), -; (11:10:17.104), -100 (11:14:24.924), +10 (00:00:00)</t>
+        <t>-; (10:50:48.660), -; (11:10:17.104), -100 (11:14:24.924) ~0.67, +10 (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E81" authorId="0" shapeId="0">
@@ -902,7 +902,7 @@
     </comment>
     <comment ref="O81" authorId="0" shapeId="0">
       <text>
-        <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+        <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q81" authorId="0" shapeId="0">
@@ -927,12 +927,12 @@
     </comment>
     <comment ref="M82" authorId="0" shapeId="0">
       <text>
-        <t>-&lt; (10:12:37.377), -/ (10:12:37.545), -head (10:12:38.381), -&gt; (10:12:38.657), +&lt; (00:00:00), +/ (00:00:00), +head (00:00:00), +&gt; (00:00:00)</t>
+        <t>-&lt; (10:12:37.377) ~1.00, -/ (10:12:37.545) ~1.00, -head (10:12:38.381) ~1.00, -&gt; (10:12:38.657) ~1.00, +&lt; (00:00:00), +/ (00:00:00), +head (00:00:00), +&gt; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="O82" authorId="0" shapeId="0">
       <text>
-        <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+        <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="E83" authorId="0" shapeId="0">
@@ -952,12 +952,12 @@
     </comment>
     <comment ref="O83" authorId="0" shapeId="0">
       <text>
-        <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+        <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
       </text>
     </comment>
     <comment ref="Q83" authorId="0" shapeId="0">
       <text>
-        <t>-bar (10:42:30.607), -. (10:42:30.785), -classList (10:42:32.670), -. (10:42:32.869), -add (10:42:33.487), -( (10:42:33.684), -" (10:42:33.916), -bar (10:42:35.380), -" (10:42:35.625), -) (10:42:36.061), -; (10:42:36.565), -bar (10:50:10.577), -. (10:50:10.720), -style (10:50:11.842), -. (10:50:12.547), -height (10:50:14.172), -= (10:50:15.244), -array (10:50:17.753), -[ (10:50:17.905), -i (10:50:18.168), -] (10:50:18.460), -* (10:50:28.020), -100 (10:50:29.694), -+ (10:50:38.934), -" (10:50:40.368), -% (10:50:40.883), -" (10:50:41.432), -; (10:50:48.660), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -; (11:10:17.104), +bar (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +add (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +bar (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +* (00:00:00), +100 (00:00:00), ++ (00:00:00), +" (00:00:00), +% (00:00:00), +" (00:00:00)</t>
+        <t>-bar (10:42:30.607) ~1.00, -. (10:42:30.785) ~1.00, -classList (10:42:32.670) ~1.00, -. (10:42:32.869) ~1.00, -add (10:42:33.487) ~1.00, -( (10:42:33.684) ~1.00, -" (10:42:33.916) ~1.00, -bar (10:42:35.380) ~1.00, -" (10:42:35.625) ~1.00, -) (10:42:36.061) ~1.00, -; (10:42:36.565) ~1.00, -bar (10:50:10.577) ~1.00, -. (10:50:10.720) ~1.00, -style (10:50:11.842) ~1.00, -. (10:50:12.547) ~1.00, -height (10:50:14.172) ~1.00, -= (10:50:15.244) ~1.00, -array (10:50:17.753) ~1.00, -[ (10:50:17.905) ~1.00, -i (10:50:18.168) ~1.00, -] (10:50:18.460) ~1.00, -* (10:50:28.020) ~1.00, -100 (10:50:29.694) ~1.00, -+ (10:50:38.934) ~1.00, -" (10:50:40.368) ~1.00, -% (10:50:40.883) ~1.00, -" (10:50:41.432) ~1.00, -; (10:50:48.660), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -; (11:10:17.104), +bar (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +add (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +bar (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +* (00:00:00), +100 (00:00:00), ++ (00:00:00), +" (00:00:00), +% (00:00:00), +" (00:00:00)</t>
       </text>
     </comment>
   </commentList>
@@ -1524,7 +1524,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-} (10:20:03.095), -flex (10:21:58.800), -direction (10:22:01.758), -column (10:22:03.223), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342), -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +justify (00:00:00), +content (00:00:00), +center (00:00:00), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-} (10:20:03.095) ~1.00, -flex (10:21:58.800) ~0.00, -direction (10:22:01.758) ~0.11, -column (10:22:03.223) ~0.17, +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342) ~1.00, -flex (10:57:30.392) ~1.00, -- (10:57:30.402) ~1.00, -end (10:57:30.432) ~0.00, -; (10:57:30.442) ~1.00, +justify (00:00:00), +content (00:00:00), +center (00:00:00), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>-i (10:38:53.739), -array (10:38:55.446), -createElement (10:39:45.021), -function (10:57:37.492), -bubbleSort (10:57:42.836), -( (10:57:43.053), -arr (10:57:49.140), -) (10:57:49.861), -{ (10:57:54.715), -} (10:58:35.895), -let (10:59:27.295), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -} (11:08:40.006), -( (11:09:55.956), -let (11:09:56.455), -i (11:09:56.677), -= (11:09:57.008), -0 (11:09:57.490), -; (11:09:57.512), -i (11:09:57.854), -&lt; (11:09:58.223), -bars (11:09:58.993), -. (11:09:59.214), -length (11:10:00.426), -; (11:10:00.634), -i (11:10:01.376), -+ (11:10:01.600), -+ (11:10:01.789), -) (11:10:01.880), -{ (11:10:02.609), -} (11:10:03.305), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -async (11:15:16.100), +1 (00:00:00), +arry (00:00:00), +cretaeElement (00:00:00), +function (00:00:00), +bubbleSort (00:00:00), +( (00:00:00), +arr (00:00:00), +) (00:00:00), +{ (00:00:00)</t>
+          <t>-i (10:38:53.739), -array (10:38:55.446) ~0.80, -createElement (10:39:45.021) ~0.85, -function (10:57:37.492) ~1.00, -bubbleSort (10:57:42.836) ~1.00, -( (10:57:43.053) ~1.00, -arr (10:57:49.140) ~1.00, -) (10:57:49.861) ~1.00, -{ (10:57:54.715) ~1.00, -} (10:58:35.895), -let (10:59:27.295), -; (11:01:05.017), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -} (11:08:40.006), -( (11:09:55.956), -let (11:09:56.455), -i (11:09:56.677), -= (11:09:57.008), -0 (11:09:57.490), -; (11:09:57.512), -i (11:09:57.854) ~0.00, -&lt; (11:09:58.223), -bars (11:09:58.993), -. (11:09:59.214), -length (11:10:00.426), -; (11:10:00.634), -i (11:10:01.376), -+ (11:10:01.600), -+ (11:10:01.789), -) (11:10:01.880), -{ (11:10:02.609), -} (11:10:03.305), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -async (11:15:16.100), +1 (00:00:00), +arry (00:00:00), +cretaeElement (00:00:00), +function (00:00:00), +bubbleSort (00:00:00), +( (00:00:00), +arr (00:00:00), +) (00:00:00), +{ (00:00:00)</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+          <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>-var (10:59:12.196), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -} (11:08:40.006), +let (00:00:00)</t>
+          <t>-var (10:59:12.196) ~0.00, +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -} (11:08:40.006), +let (00:00:00)</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-Visualizer (10:12:47.677), -Visualizer (10:13:16.993), +visualizer (00:00:00), +visualizer (00:00:00)</t>
+          <t>-Visualizer (10:12:47.677) ~0.90, -Visualizer (10:13:16.993) ~0.90, +visualizer (00:00:00), +visualizer (00:00:00)</t>
         </is>
       </c>
       <c r="O9" t="n">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-} (10:17:11.029), -} (10:20:03.095), -flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00)</t>
+          <t>-} (10:17:11.029) ~1.00, -} (10:20:03.095) ~1.00, -flex (10:21:58.800) ~1.00, -- (10:21:58.984) ~1.00, -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +display (00:00:00), +: (00:00:00), +flex (00:00:00), +; (00:00:00), +} (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>+bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -; (11:08:34.198), -updateBars (11:08:38.342), -getElementsByClassName (11:09:28.891), +function (00:00:00), +{ (00:00:00), +updatebars (00:00:00), +getElementByClassName (00:00:00), +} (00:00:00)</t>
+          <t>+bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -; (11:08:34.198) ~0.00, -updateBars (11:08:38.342) ~0.90, -getElementsByClassName (11:09:28.891) ~0.95, +function (00:00:00), +{ (00:00:00), +updatebars (00:00:00), +getElementByClassName (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+          <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q12" t="n">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>-&lt; (10:12:43.632), -title (10:12:44.512), -&gt; (10:12:44.622), -Sorting (10:12:45.778), -Visualizer (10:12:47.677), -&lt; (10:12:47.904), -/ (10:12:48.260), -title (10:12:49.434), -&gt; (10:12:49.841), +&lt; (00:00:00), +title (00:00:00), +&gt; (00:00:00), +Sorting (00:00:00), +Visualizer (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +title (00:00:00), +&gt; (00:00:00)</t>
+          <t>-&lt; (10:12:43.632) ~1.00, -title (10:12:44.512) ~1.00, -&gt; (10:12:44.622) ~1.00, -Sorting (10:12:45.778) ~1.00, -Visualizer (10:12:47.677) ~1.00, -&lt; (10:12:47.904) ~1.00, -/ (10:12:48.260) ~1.00, -title (10:12:49.434) ~1.00, -&gt; (10:12:49.841) ~1.00, +&lt; (00:00:00), +title (00:00:00), +&gt; (00:00:00), +Sorting (00:00:00), +Visualizer (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +title (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="O19" t="n">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+          <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q19" t="n">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>-} (10:39:17.549), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -; (11:14:32.118), +} (00:00:00)</t>
+          <t>-} (10:39:17.549) ~1.00, +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -; (11:14:32.118), +} (00:00:00)</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>-Visualizer (10:12:47.677), +Visualiser (00:00:00)</t>
+          <t>-Visualizer (10:12:47.677) ~0.90, +Visualiser (00:00:00)</t>
         </is>
       </c>
       <c r="O21" t="n">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), -0px (10:48:03.827), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +0 (00:00:00)</t>
+          <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, -0px (10:48:03.827) ~0.33, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +0 (00:00:00)</t>
         </is>
       </c>
       <c r="Q21" t="n">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>-getElementsByClassName (11:09:28.891), -bars (11:09:58.993), -100 (11:14:24.924), +querySelectorAll (00:00:00), +. (00:00:00), +array (00:00:00), +10 (00:00:00)</t>
+          <t>-getElementsByClassName (11:09:28.891) ~0.18, -bars (11:09:58.993) ~0.20, -100 (11:14:24.924) ~0.67, +querySelectorAll (00:00:00), +. (00:00:00), +array (00:00:00), +10 (00:00:00)</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), -. (10:43:24.242), -bar (10:43:31.288), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +. (00:00:00), +bar (00:00:00)</t>
+          <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, -. (10:43:24.242) ~1.00, -bar (10:43:31.288) ~1.00, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +. (00:00:00), +bar (00:00:00)</t>
         </is>
       </c>
       <c r="Q24" t="n">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+          <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q25" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>-length (10:38:57.372), -classList (10:42:32.670), -length (10:59:32.061), -getElementsByClassName (11:09:28.891), -length (11:10:00.426), -Promise (11:13:54.982), +lenght (00:00:00), +ClassList (00:00:00), +getElementByClassName (00:00:00), +lenght (00:00:00), +lenght (00:00:00), +promise (00:00:00)</t>
+          <t>-length (10:38:57.372) ~0.67, -classList (10:42:32.670) ~0.89, -length (10:59:32.061) ~0.67, -getElementsByClassName (11:09:28.891) ~0.95, -length (11:10:00.426) ~0.67, -Promise (11:13:54.982) ~0.86, +lenght (00:00:00), +ClassList (00:00:00), +getElementByClassName (00:00:00), +lenght (00:00:00), +lenght (00:00:00), +promise (00:00:00)</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+          <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q30" t="n">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>-Sorting (10:12:45.778), +sorting (00:00:00)</t>
+          <t>-Sorting (10:12:45.778) ~0.86, +sorting (00:00:00)</t>
         </is>
       </c>
       <c r="O31" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+          <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q31" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>-for (10:59:26.374), -( (10:59:26.727), -let (10:59:27.295), -i (10:59:27.677), -= (10:59:27.952), -1 (10:59:28.458), -; (10:59:28.738), -i (10:59:29.253), -&lt; (10:59:29.652), -arr (10:59:30.525), -. (10:59:30.766), -length (10:59:32.061), -; (10:59:32.305), -i (10:59:32.661), -+ (10:59:32.869), -+ (10:59:33.126), -) (10:59:33.350), -{ (10:59:35.506), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +arr (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00)</t>
+          <t>-for (10:59:26.374) ~1.00, -( (10:59:26.727) ~1.00, -let (10:59:27.295) ~1.00, -i (10:59:27.677) ~1.00, -= (10:59:27.952) ~1.00, -1 (10:59:28.458) ~0.00, -; (10:59:28.738) ~1.00, -i (10:59:29.253) ~1.00, -&lt; (10:59:29.652) ~1.00, -arr (10:59:30.525) ~1.00, -. (10:59:30.766) ~1.00, -length (10:59:32.061) ~1.00, -; (10:59:32.305) ~1.00, -i (10:59:32.661) ~1.00, -+ (10:59:32.869) ~1.00, -+ (10:59:33.126) ~1.00, -) (10:59:33.350) ~1.00, -{ (10:59:35.506) ~1.00, +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +arr (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00)</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-Sorting (10:13:13.802), +/ (00:00:00), +sorting (00:00:00)</t>
+          <t>-Sorting (10:13:13.802) ~0.86, +/ (00:00:00), +sorting (00:00:00)</t>
         </is>
       </c>
       <c r="O36" t="n">
@@ -3106,7 +3106,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+          <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q36" t="n">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>-50 (10:27:50.527), -. (10:31:30.292), -. (10:38:55.684), -. (10:40:28.151), -arr (11:01:09.861), -; (11:01:10.683), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -; (11:10:17.104), -Promise (11:13:54.982), +20 (00:00:00), +, (00:00:00), +bubblesort (00:00:00), +, (00:00:00), +, (00:00:00), +aee (00:00:00), +promise (00:00:00)</t>
+          <t>-50 (10:27:50.527) ~0.50, -. (10:31:30.292) ~0.00, -. (10:38:55.684) ~0.00, -. (10:40:28.151) ~0.00, -arr (11:01:09.861) ~0.33, -; (11:01:10.683), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -; (11:10:17.104), -Promise (11:13:54.982) ~0.86, +20 (00:00:00), +, (00:00:00), +bubblesort (00:00:00), +, (00:00:00), +, (00:00:00), +aee (00:00:00), +promise (00:00:00)</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +coloumn (00:00:00), +; (00:00:00)</t>
+          <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952), -column (10:22:03.223) ~0.86, -; (10:22:03.455) ~1.00, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +coloumn (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q42" t="n">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>-let (10:38:51.733), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -let (11:09:56.455), -bars (11:09:58.993), -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -updateBars (11:12:30.664), -( (11:12:30.752), -) (11:12:30.906), -; (11:12:31.204), -await (11:13:47.348), -new (11:13:53.570), -Promise (11:13:54.982), -( (11:13:55.301), -resolve (11:13:59.055), -= (11:14:16.118), -&gt; (11:14:16.408), -setTimeout (11:14:18.857), -( (11:14:19.066), -resolve (11:14:23.324), -, (11:14:23.491), -100 (11:14:24.924), -) (11:14:31.103), -) (11:14:31.475), -; (11:14:32.118), -async (11:15:16.100), +array (00:00:00)</t>
+          <t>-let (10:38:51.733), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -let (11:09:56.455), -bars (11:09:58.993) ~0.20, -bars (11:10:05.954), -[ (11:10:06.083), -i (11:10:06.207), -] (11:10:06.517), -. (11:10:06.753), -style (11:10:08.322), -. (11:10:08.474), -height (11:10:09.606), -= (11:10:12.868), -array (11:10:13.726), -[ (11:10:13.999), -i (11:10:14.138), -] (11:10:14.279), -* (11:10:14.846), -100 (11:10:15.517), -+ (11:10:16.137), -" (11:10:16.502), -% (11:10:16.625), -" (11:10:16.705), -; (11:10:17.104), -updateBars (11:12:30.664), -( (11:12:30.752), -) (11:12:30.906), -; (11:12:31.204), -await (11:13:47.348), -new (11:13:53.570), -Promise (11:13:54.982), -( (11:13:55.301), -resolve (11:13:59.055), -= (11:14:16.118), -&gt; (11:14:16.408), -setTimeout (11:14:18.857), -( (11:14:19.066), -resolve (11:14:23.324), -, (11:14:23.491), -100 (11:14:24.924), -) (11:14:31.103), -) (11:14:31.475), -; (11:14:32.118), -async (11:15:16.100), +array (00:00:00)</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+          <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q45" t="n">
@@ -3522,7 +3522,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>-} (10:39:17.549), -; (11:10:17.104), +} (00:00:00)</t>
+          <t>-} (10:39:17.549) ~1.00, -; (11:10:17.104), +} (00:00:00)</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), -display (10:47:38.305), -flex (10:47:39.551), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +red* (10:50:09.332), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+          <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, -display (10:47:38.305), -flex (10:47:39.551), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +red* (10:50:09.332), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q46" t="n">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>-title (10:12:49.434), -Visualizer (10:13:16.993), +tittle (00:00:00), +visualizer (00:00:00)</t>
+          <t>-title (10:12:49.434) ~0.83, -Visualizer (10:13:16.993) ~0.90, +tittle (00:00:00), +visualizer (00:00:00)</t>
         </is>
       </c>
       <c r="O48" t="n">
@@ -3690,7 +3690,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>-} (10:20:03.095), -flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), -display (10:47:38.305), -flex (10:47:39.551), -; (10:47:39.811), -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), -; (10:48:07.569), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +red* (10:50:09.332), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342), -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-} (10:20:03.095) ~1.00, -flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, -display (10:47:38.305), -flex (10:47:39.551), -; (10:47:39.811), -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), -; (10:48:07.569), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +red* (10:50:09.332), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342) ~1.00, -flex (10:57:30.392) ~1.00, -- (10:57:30.402) ~1.00, -end (10:57:30.432) ~0.11, -; (10:57:30.442), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="Q48" t="n">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>-array (10:28:45.898), -const (10:37:42.386), -visualizer (10:37:44.631), -= (10:37:45.082), -document (10:37:47.323), -. (10:37:47.760), -getElementById (10:38:03.158), -" (10:38:19.019), -vis (10:38:19.926), -- (10:38:20.217), -123456 (10:38:22.251), -" (10:38:22.629), +bubbleSort* (11:08:31.581), -array (11:08:34.178), -getElementsByClassName (11:09:28.891), +arry (00:00:00), +arry (00:00:00), +const (00:00:00), +visualizer (00:00:00), += (00:00:00), +documnet (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
+          <t>-array (10:28:45.898) ~0.80, -const (10:37:42.386) ~1.00, -visualizer (10:37:44.631) ~1.00, -= (10:37:45.082) ~1.00, -document (10:37:47.323) ~0.75, -. (10:37:47.760) ~1.00, -getElementById (10:38:03.158) ~1.00, -" (10:38:19.019) ~1.00, -vis (10:38:19.926) ~1.00, -- (10:38:20.217) ~1.00, -123456 (10:38:22.251) ~1.00, -" (10:38:22.629) ~1.00, +bubbleSort* (11:08:31.581), -array (11:08:34.178) ~0.80, -getElementsByClassName (11:09:28.891) ~0.95, +arry (00:00:00), +arry (00:00:00), +const (00:00:00), +visualizer (00:00:00), += (00:00:00), +documnet (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +123456 (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>-html (10:12:23.484), +htm (00:00:00)</t>
+          <t>-html (10:12:23.484) ~0.75, +htm (00:00:00)</t>
         </is>
       </c>
       <c r="O50" t="n">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>-} (10:20:03.095), -flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), -- (10:57:30.402), -end (10:57:30.432), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-} (10:20:03.095) ~1.00, -flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, -- (10:57:30.402) ~1.00, -end (10:57:30.432) ~0.11, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="Q50" t="n">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>-bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -getElementsByClassName (11:09:28.891), -100 (11:14:24.924), +getElementsByClassname (00:00:00), +10 (00:00:00)</t>
+          <t>-bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -getElementsByClassName (11:09:28.891) ~0.95, -100 (11:14:24.924) ~0.67, +getElementsByClassname (00:00:00), +10 (00:00:00)</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+          <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q51" t="n">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>-&lt; (10:12:43.632), -title (10:12:44.512), -&gt; (10:12:44.622), -&lt; (10:12:47.904), -/ (10:12:48.260), -title (10:12:49.434), -&gt; (10:12:49.841), -Sorting (10:13:13.802), -Visualizer (10:13:16.993), -&lt; (10:13:17.335), -/ (10:13:17.789), -h1 (10:13:18.123), -&gt; (10:13:18.254), +Sorting (00:00:00), +Visualizer (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +h1 (00:00:00), +&gt; (00:00:00)</t>
+          <t>-&lt; (10:12:43.632), -title (10:12:44.512), -&gt; (10:12:44.622), -&lt; (10:12:47.904), -/ (10:12:48.260), -title (10:12:49.434), -&gt; (10:12:49.841), -Sorting (10:13:13.802) ~1.00, -Visualizer (10:13:16.993) ~1.00, -&lt; (10:13:17.335) ~1.00, -/ (10:13:17.789) ~1.00, -h1 (10:13:18.123) ~1.00, -&gt; (10:13:18.254) ~1.00, +Sorting (00:00:00), +Visualizer (00:00:00), +&lt; (00:00:00), +/ (00:00:00), +h1 (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="O56" t="n">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+          <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q56" t="n">
@@ -4114,7 +4114,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>-; (10:50:48.660), -100 (11:14:24.924), +10 (00:00:00)</t>
+          <t>-; (10:50:48.660), -100 (11:14:24.924) ~0.67, +10 (00:00:00)</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>-} (10:20:03.095), -flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342), -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +flex (00:00:00), +- (00:00:00), +end (00:00:00), +; (00:00:00), +} (00:00:00)</t>
+          <t>-} (10:20:03.095) ~1.00, -flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952), -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, -align (10:57:30.272) ~1.00, -- (10:57:30.282) ~1.00, -items (10:57:30.332), -: (10:57:30.342) ~1.00, -flex (10:57:30.392) ~1.00, -- (10:57:30.402) ~1.00, -end (10:57:30.432) ~1.00, -; (10:57:30.442) ~1.00, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +align (00:00:00), +- (00:00:00), +items (00:00:00), +: (00:00:00), +flex (00:00:00), +- (00:00:00), +end (00:00:00), +; (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="Q59" t="n">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>-length (10:38:57.372), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -getElementsByClassName (11:09:28.891), -; (11:14:32.118), +lenght (00:00:00), +getElementsByClassname (00:00:00)</t>
+          <t>-length (10:38:57.372) ~0.67, +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -getElementsByClassName (11:09:28.891) ~0.95, -; (11:14:32.118), +lenght (00:00:00), +getElementsByClassname (00:00:00)</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+          <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q62" t="n">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>-} (10:20:03.095), -flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), -7px (10:43:39.527), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +} (00:00:00), +700px (00:00:00)</t>
+          <t>-} (10:20:03.095) ~1.00, -flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, -7px (10:43:39.527) ~0.60, +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +} (00:00:00), +700px (00:00:00)</t>
         </is>
       </c>
       <c r="Q66" t="n">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>-height (10:20:07.891), -: (10:20:07.983), -200px (10:20:09.051), -; (10:20:09.451), -0px (10:48:03.827), +;* (10:50:09.333), +height (00:00:00), +: (00:00:00), +200px (00:00:00), +background (00:00:00), +: (00:00:00), +red (00:00:00), +; (00:00:00), +0 (00:00:00)</t>
+          <t>-height (10:20:07.891) ~1.00, -: (10:20:07.983) ~1.00, -200px (10:20:09.051) ~1.00, -; (10:20:09.451), -0px (10:48:03.827) ~0.33, +;* (10:50:09.333), +height (00:00:00), +: (00:00:00), +200px (00:00:00), +background (00:00:00), +: (00:00:00), +red (00:00:00), +; (00:00:00), +0 (00:00:00)</t>
         </is>
       </c>
       <c r="Q68" t="n">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>-function (10:57:37.492), -bubbleSort (10:57:42.836), -( (10:57:43.053), -arr (10:57:49.140), -) (10:57:49.861), -{ (10:57:54.715), -1 (10:59:28.458), -- (10:59:44.058), -1 (10:59:44.656), -- (11:01:07.252), -1 (11:01:07.757), -bubbleSort (11:08:34.118), -array (11:08:34.178), -function (11:08:36.630), -updateBars (11:08:38.342), -( (11:08:38.511), -) (11:08:38.687), -{ (11:08:39.319), -const (11:09:21.850), -bars (11:09:22.876), -= (11:09:23.405), -document (11:09:24.920), -. (11:09:25.072), -getElementsByClassName (11:09:28.891), -( (11:09:28.949), -" (11:09:29.056), -bar (11:09:29.764), -" (11:09:29.897), -) (11:09:29.998), -; (11:09:30.476), -for (11:09:55.616), -( (11:09:55.956), -let (11:09:56.455), -i (11:09:56.677), -= (11:09:57.008), -0 (11:09:57.490), -; (11:09:57.512), -i (11:09:57.854), -&lt; (11:09:58.223), -bars (11:09:58.993), -. (11:09:59.214), -length (11:10:00.426), -; (11:10:00.634), -i (11:10:01.376), -+ (11:10:01.600), -+ (11:10:01.789), -) (11:10:01.880), -{ (11:10:02.609), -updateBars (11:12:30.664), -await (11:13:47.348), -new (11:13:53.570), -Promise (11:13:54.982), -( (11:13:55.301), -resolve (11:13:59.055), -= (11:14:16.118), -&gt; (11:14:16.408), -setTimeout (11:14:18.857), -( (11:14:19.066), -resolve (11:14:23.324), -, (11:14:23.491), -100 (11:14:24.924), -) (11:14:31.103), -) (11:14:31.475), -; (11:14:32.118), -async (11:15:16.100), +function (00:00:00), +updataBars (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +visualizer (00:00:00), +. (00:00:00), +querySelectorAll (00:00:00), +" (00:00:00), +. (00:00:00), +bar (00:00:00), +" (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +array (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +async (00:00:00), +function (00:00:00), +bubblesort (00:00:00), +( (00:00:00), +arr (00:00:00), +) (00:00:00), +{ (00:00:00), +0 (00:00:00), +- (00:00:00), +1 (00:00:00), ++ (00:00:00), +1 (00:00:00), ++ (00:00:00), +1 (00:00:00), ++ (00:00:00), +1 (00:00:00), +updataBars (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +10 (00:00:00), +) (00:00:00)</t>
+          <t>-function (10:57:37.492) ~1.00, -bubbleSort (10:57:42.836) ~0.90, -( (10:57:43.053) ~1.00, -arr (10:57:49.140) ~1.00, -) (10:57:49.861) ~1.00, -{ (10:57:54.715) ~1.00, -1 (10:59:28.458) ~0.00, -- (10:59:44.058), -1 (10:59:44.656) ~1.00, -- (11:01:07.252) ~0.00, -1 (11:01:07.757) ~1.00, -bubbleSort (11:08:34.118) ~0.20, -array (11:08:34.178), -function (11:08:36.630), -updateBars (11:08:38.342) ~0.90, -( (11:08:38.511) ~1.00, -) (11:08:38.687) ~1.00, -{ (11:08:39.319) ~1.00, -const (11:09:21.850) ~1.00, -bars (11:09:22.876) ~1.00, -= (11:09:23.405) ~1.00, -document (11:09:24.920) ~0.10, -. (11:09:25.072) ~1.00, -getElementsByClassName (11:09:28.891) ~0.18, -( (11:09:28.949) ~0.00, -" (11:09:29.056) ~1.00, -bar (11:09:29.764) ~1.00, -" (11:09:29.897) ~1.00, -) (11:09:29.998), -; (11:09:30.476), -for (11:09:55.616) ~1.00, -( (11:09:55.956) ~1.00, -let (11:09:56.455) ~1.00, -i (11:09:56.677) ~1.00, -= (11:09:57.008) ~1.00, -0 (11:09:57.490) ~1.00, -; (11:09:57.512) ~1.00, -i (11:09:57.854) ~1.00, -&lt; (11:09:58.223) ~1.00, -bars (11:09:58.993) ~0.20, -. (11:09:59.214) ~1.00, -length (11:10:00.426) ~1.00, -; (11:10:00.634) ~1.00, -i (11:10:01.376) ~1.00, -+ (11:10:01.600) ~1.00, -+ (11:10:01.789) ~1.00, -) (11:10:01.880) ~1.00, -{ (11:10:02.609) ~1.00, -updateBars (11:12:30.664) ~0.90, -await (11:13:47.348) ~1.00, -new (11:13:53.570) ~1.00, -Promise (11:13:54.982) ~1.00, -( (11:13:55.301) ~1.00, -resolve (11:13:59.055) ~1.00, -= (11:14:16.118) ~1.00, -&gt; (11:14:16.408) ~1.00, -setTimeout (11:14:18.857) ~1.00, -( (11:14:19.066) ~1.00, -resolve (11:14:23.324) ~1.00, -, (11:14:23.491) ~1.00, -100 (11:14:24.924) ~0.67, -) (11:14:31.103) ~1.00, -) (11:14:31.475), -; (11:14:32.118), -async (11:15:16.100) ~1.00, +function (00:00:00), +updataBars (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +const (00:00:00), +bars (00:00:00), += (00:00:00), +visualizer (00:00:00), +. (00:00:00), +querySelectorAll (00:00:00), +" (00:00:00), +. (00:00:00), +bar (00:00:00), +" (00:00:00), +for (00:00:00), +( (00:00:00), +let (00:00:00), +i (00:00:00), += (00:00:00), +0 (00:00:00), +; (00:00:00), +i (00:00:00), +&lt; (00:00:00), +array (00:00:00), +. (00:00:00), +length (00:00:00), +; (00:00:00), +i (00:00:00), ++ (00:00:00), ++ (00:00:00), +) (00:00:00), +{ (00:00:00), +async (00:00:00), +function (00:00:00), +bubblesort (00:00:00), +( (00:00:00), +arr (00:00:00), +) (00:00:00), +{ (00:00:00), +0 (00:00:00), +- (00:00:00), +1 (00:00:00), ++ (00:00:00), +1 (00:00:00), ++ (00:00:00), +1 (00:00:00), ++ (00:00:00), +1 (00:00:00), +updataBars (00:00:00), +( (00:00:00), +) (00:00:00), +; (00:00:00), +await (00:00:00), +new (00:00:00), +Promise (00:00:00), +resolve (00:00:00), += (00:00:00), +&gt; (00:00:00), +setTimeout (00:00:00), +( (00:00:00), +resolve (00:00:00), +, (00:00:00), +10 (00:00:00), +) (00:00:00)</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>-DOCTYPE (10:12:14.338), -Visualizer (10:12:47.677), -Sorting (10:13:13.802), -Visualizer (10:13:16.993), -&lt; (10:27:15.917), +Doctype (00:00:00), +visualizer (00:00:00), +sorting (00:00:00), +visualizer (00:00:00)</t>
+          <t>-DOCTYPE (10:12:14.338) ~0.14, -Visualizer (10:12:47.677) ~0.90, -Sorting (10:13:13.802) ~0.86, -Visualizer (10:13:16.993) ~0.90, -&lt; (10:27:15.917), +Doctype (00:00:00), +visualizer (00:00:00), +sorting (00:00:00), +visualizer (00:00:00)</t>
         </is>
       </c>
       <c r="O70" t="n">
@@ -4820,7 +4820,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>-200px (10:20:09.051), -flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), -background (10:44:24.231), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +500px (00:00:00), +Background (00:00:00)</t>
+          <t>-200px (10:20:09.051) ~0.80, -flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, -background (10:44:24.231) ~0.90, +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +500px (00:00:00), +Background (00:00:00)</t>
         </is>
       </c>
       <c r="Q70" t="n">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>-bubbleSort (10:57:42.836), -i (10:59:29.253), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -&lt; (11:09:58.223), -bars (11:09:58.993), -i (11:10:01.376), -Promise (11:13:54.982), +&gt; (00:00:00), +bats (00:00:00), +bubblesort (00:00:00), +promise (00:00:00)</t>
+          <t>-bubbleSort (10:57:42.836) ~0.90, -i (10:59:29.253), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -&lt; (11:09:58.223) ~0.00, -bars (11:09:58.993) ~0.75, -i (11:10:01.376), -Promise (11:13:54.982) ~0.86, +&gt; (00:00:00), +bats (00:00:00), +bubblesort (00:00:00), +promise (00:00:00)</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+          <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q71" t="n">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>-title (10:12:49.434), -Visualizer (10:13:16.993), -123456 (10:18:40.665), +tittle (00:00:00), +visualizer (00:00:00), +654321 (00:00:00)</t>
+          <t>-title (10:12:49.434) ~0.83, -Visualizer (10:13:16.993) ~0.90, -123456 (10:18:40.665) ~0.00, +tittle (00:00:00), +visualizer (00:00:00), +654321 (00:00:00)</t>
         </is>
       </c>
       <c r="O72" t="n">
@@ -4964,7 +4964,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>-# (10:19:53.296), -vis (10:19:54.003), -- (10:19:54.226), -123456 (10:19:55.544), -{ (10:20:02.452), -} (10:20:03.095), -flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), -display (10:47:38.305), -flex (10:47:39.551), -; (10:47:39.811), -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), -; (10:48:07.569), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +red* (10:50:09.332), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342), -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +654321 (00:00:00), +{ (00:00:00), +} (00:00:00)</t>
+          <t>-# (10:19:53.296) ~1.00, -vis (10:19:54.003) ~1.00, -- (10:19:54.226) ~1.00, -123456 (10:19:55.544) ~0.00, -{ (10:20:02.452) ~1.00, -} (10:20:03.095) ~1.00, -flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, -display (10:47:38.305), -flex (10:47:39.551), -; (10:47:39.811), -margin (10:48:02.482), -: (10:48:02.549), -0px (10:48:03.827), -1px (10:48:07.241), -; (10:48:07.569), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +red* (10:50:09.332), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342) ~1.00, -flex (10:57:30.392) ~1.00, -- (10:57:30.402) ~1.00, -end (10:57:30.432) ~0.11, -; (10:57:30.442), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00), +# (00:00:00), +vis (00:00:00), +- (00:00:00), +654321 (00:00:00), +{ (00:00:00), +} (00:00:00)</t>
         </is>
       </c>
       <c r="Q72" t="n">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>-array (10:28:45.898), -const (10:37:42.386), -visualizer (10:37:44.631), -= (10:37:45.082), -document (10:37:47.323), -. (10:37:47.760), -getElementById (10:38:03.158), -" (10:38:19.019), -vis (10:38:19.926), -- (10:38:20.217), -123456 (10:38:22.251), -" (10:38:22.629), +bubbleSort* (11:08:31.581), -array (11:08:34.178), -getElementsByClassName (11:09:28.891), +arry (00:00:00), +arry (00:00:00), +const (00:00:00), +visualizer (00:00:00), += (00:00:00), +documnet (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +654321 (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
+          <t>-array (10:28:45.898) ~0.80, -const (10:37:42.386) ~1.00, -visualizer (10:37:44.631) ~1.00, -= (10:37:45.082) ~1.00, -document (10:37:47.323) ~0.75, -. (10:37:47.760) ~1.00, -getElementById (10:38:03.158) ~1.00, -" (10:38:19.019) ~1.00, -vis (10:38:19.926) ~1.00, -- (10:38:20.217) ~1.00, -123456 (10:38:22.251) ~0.00, -" (10:38:22.629) ~1.00, +bubbleSort* (11:08:31.581), -array (11:08:34.178) ~0.80, -getElementsByClassName (11:09:28.891) ~0.95, +arry (00:00:00), +arry (00:00:00), +const (00:00:00), +visualizer (00:00:00), += (00:00:00), +documnet (00:00:00), +. (00:00:00), +getElementById (00:00:00), +( (00:00:00), +" (00:00:00), +vis (00:00:00), +- (00:00:00), +654321 (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +arry (00:00:00), +getElementByClassName (00:00:00)</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
@@ -5038,7 +5038,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+          <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q73" t="n">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342), -flex (10:57:30.392), -- (10:57:30.402), -end (10:57:30.432), -; (10:57:30.442), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+          <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, +width* (10:50:08.733), +:* (10:50:08.734), +200px* (10:50:08.740), +;* (10:50:08.741), +background* (10:50:09.321), +-* (10:50:09.322), +color* (10:50:09.327), +:* (10:50:09.328), +red* (10:50:09.332), +;* (10:50:09.333), -align (10:57:30.272), -- (10:57:30.282), -items (10:57:30.332), -: (10:57:30.342) ~1.00, -flex (10:57:30.392) ~1.00, -- (10:57:30.402) ~1.00, -end (10:57:30.432) ~0.11, -; (10:57:30.442), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q75" t="n">
@@ -5150,7 +5150,7 @@
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>-createElement (10:39:45.021), -visualizer (10:40:27.992), -. (10:40:28.151), -appendChild (10:40:30.229), -( (10:40:30.435), -bar (10:40:31.317), -) (10:40:31.505), -; (10:40:32.101), -bubbleSort (10:57:42.836), -&gt; (10:59:45.546), -arr (10:59:46.616), -[ (10:59:46.969), -i (10:59:47.212), -] (10:59:47.751), -- (11:01:03.607), -1 (11:01:04.198), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -function (11:08:36.630), -updateBars (11:08:38.342), -( (11:08:38.511), -) (11:08:38.687), -{ (11:08:39.319), -getElementsByClassName (11:09:28.891), -; (11:09:57.512), -i (11:09:57.854), -bars (11:09:58.993), -} (11:10:03.305), -setTimeout (11:14:18.857), +createrElement (00:00:00), +function (00:00:00), +updatebars (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +get (00:00:00), +ElementsByClassName (00:00:00), +array (00:00:00), +bubblesort (00:00:00), +setTimeOut (00:00:00)</t>
+          <t>-createElement (10:39:45.021) ~0.93, -visualizer (10:40:27.992), -. (10:40:28.151), -appendChild (10:40:30.229), -( (10:40:30.435), -bar (10:40:31.317), -) (10:40:31.505), -; (10:40:32.101), -bubbleSort (10:57:42.836) ~0.90, -&gt; (10:59:45.546), -arr (10:59:46.616), -[ (10:59:46.969), -i (10:59:47.212), -] (10:59:47.751), -- (11:01:03.607), -1 (11:01:04.198), -arr (11:01:06.389), -[ (11:01:06.650), -i (11:01:06.835), -- (11:01:07.252), -1 (11:01:07.757), -] (11:01:08.184), -= (11:01:08.961), -arr (11:01:09.861), -[ (11:01:10.052), -i (11:01:10.368), -] (11:01:10.513), -; (11:01:10.683), -bubbleSort (11:08:34.118), -( (11:08:34.128) ~1.00, -array (11:08:34.178), -) (11:08:34.188) ~1.00, -; (11:08:34.198), -function (11:08:36.630) ~1.00, -updateBars (11:08:38.342) ~0.90, -( (11:08:38.511), -) (11:08:38.687), -{ (11:08:39.319) ~1.00, -getElementsByClassName (11:09:28.891) ~0.86, -; (11:09:57.512), -i (11:09:57.854), -bars (11:09:58.993) ~0.20, -} (11:10:03.305), -setTimeout (11:14:18.857) ~0.90, +createrElement (00:00:00), +function (00:00:00), +updatebars (00:00:00), +( (00:00:00), +) (00:00:00), +{ (00:00:00), +get (00:00:00), +ElementsByClassName (00:00:00), +array (00:00:00), +bubblesort (00:00:00), +setTimeOut (00:00:00)</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+          <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q78" t="n">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+          <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q79" t="n">
@@ -5374,7 +5374,7 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>-; (10:50:48.660), -; (11:10:17.104), -100 (11:14:24.924), +10 (00:00:00)</t>
+          <t>-; (10:50:48.660), -; (11:10:17.104), -100 (11:14:24.924) ~0.67, +10 (00:00:00)</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+          <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q81" t="n">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>-&lt; (10:12:37.377), -/ (10:12:37.545), -head (10:12:38.381), -&gt; (10:12:38.657), +&lt; (00:00:00), +/ (00:00:00), +head (00:00:00), +&gt; (00:00:00)</t>
+          <t>-&lt; (10:12:37.377) ~1.00, -/ (10:12:37.545) ~1.00, -head (10:12:38.381) ~1.00, -&gt; (10:12:38.657) ~1.00, +&lt; (00:00:00), +/ (00:00:00), +head (00:00:00), +&gt; (00:00:00)</t>
         </is>
       </c>
       <c r="O82" t="n">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+          <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q82" t="n">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>-flex (10:21:58.800), -- (10:21:58.984), -direction (10:22:01.758), -: (10:22:01.952), -column (10:22:03.223), -; (10:22:03.455), +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
+          <t>-flex (10:21:58.800) ~1.00, -- (10:21:58.984), -direction (10:22:01.758) ~1.00, -: (10:22:01.952) ~1.00, -column (10:22:03.223) ~1.00, -; (10:22:03.455) ~1.00, +flex (00:00:00), +- (00:00:00), +direction (00:00:00), +: (00:00:00), +column (00:00:00), +; (00:00:00)</t>
         </is>
       </c>
       <c r="Q83" t="n">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>-bar (10:42:30.607), -. (10:42:30.785), -classList (10:42:32.670), -. (10:42:32.869), -add (10:42:33.487), -( (10:42:33.684), -" (10:42:33.916), -bar (10:42:35.380), -" (10:42:35.625), -) (10:42:36.061), -; (10:42:36.565), -bar (10:50:10.577), -. (10:50:10.720), -style (10:50:11.842), -. (10:50:12.547), -height (10:50:14.172), -= (10:50:15.244), -array (10:50:17.753), -[ (10:50:17.905), -i (10:50:18.168), -] (10:50:18.460), -* (10:50:28.020), -100 (10:50:29.694), -+ (10:50:38.934), -" (10:50:40.368), -% (10:50:40.883), -" (10:50:41.432), -; (10:50:48.660), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -; (11:10:17.104), +bar (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +add (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +bar (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +* (00:00:00), +100 (00:00:00), ++ (00:00:00), +" (00:00:00), +% (00:00:00), +" (00:00:00)</t>
+          <t>-bar (10:42:30.607) ~1.00, -. (10:42:30.785) ~1.00, -classList (10:42:32.670) ~1.00, -. (10:42:32.869) ~1.00, -add (10:42:33.487) ~1.00, -( (10:42:33.684) ~1.00, -" (10:42:33.916) ~1.00, -bar (10:42:35.380) ~1.00, -" (10:42:35.625) ~1.00, -) (10:42:36.061) ~1.00, -; (10:42:36.565) ~1.00, -bar (10:50:10.577) ~1.00, -. (10:50:10.720) ~1.00, -style (10:50:11.842) ~1.00, -. (10:50:12.547) ~1.00, -height (10:50:14.172) ~1.00, -= (10:50:15.244) ~1.00, -array (10:50:17.753) ~1.00, -[ (10:50:17.905) ~1.00, -i (10:50:18.168) ~1.00, -] (10:50:18.460) ~1.00, -* (10:50:28.020) ~1.00, -100 (10:50:29.694) ~1.00, -+ (10:50:38.934) ~1.00, -" (10:50:40.368) ~1.00, -% (10:50:40.883) ~1.00, -" (10:50:41.432) ~1.00, -; (10:50:48.660), +bubbleSort* (11:08:31.581), +(* (11:08:31.582), +array* (11:08:31.587), +)* (11:08:31.588), +;* (11:08:31.589), -bubbleSort (11:08:34.118), -( (11:08:34.128), -array (11:08:34.178), -) (11:08:34.188), -; (11:08:34.198), -; (11:10:17.104), +bar (00:00:00), +. (00:00:00), +classList (00:00:00), +. (00:00:00), +add (00:00:00), +( (00:00:00), +" (00:00:00), +bar (00:00:00), +" (00:00:00), +) (00:00:00), +; (00:00:00), +bar (00:00:00), +. (00:00:00), +style (00:00:00), +. (00:00:00), +height (00:00:00), += (00:00:00), +array (00:00:00), +[ (00:00:00), +i (00:00:00), +] (00:00:00), +* (00:00:00), +100 (00:00:00), ++ (00:00:00), +" (00:00:00), +% (00:00:00), +" (00:00:00)</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
